--- a/EncuestaFormato.xlsx
+++ b/EncuestaFormato.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\Diseño de Tics\ANEXOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\Diseño de Tics\ANEXOS\DATC_TIC_ANEXOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13DA9E36-3012-4AA7-8E0D-38776718A603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B580322-4386-4940-910C-BFA6D1EA1AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7C4A1742-C7B5-4888-A988-BD7336482607}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="15">
   <si>
     <t>N.º</t>
   </si>
@@ -82,45 +81,6 @@
   </si>
   <si>
     <t xml:space="preserve">Pregunta </t>
-  </si>
-  <si>
-    <t>Participante</t>
-  </si>
-  <si>
-    <t>Puntuación SUS (0-100)</t>
-  </si>
-  <si>
-    <t>Calificación (Adjetiva)</t>
-  </si>
-  <si>
-    <t>Excelente</t>
-  </si>
-  <si>
-    <t>Bueno</t>
-  </si>
-  <si>
-    <t>Mejor Imaginable</t>
-  </si>
-  <si>
-    <t>Promedio Global</t>
-  </si>
-  <si>
-    <t>Grado A (Excelente)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P1 </t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>P4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P5 </t>
   </si>
 </sst>
 </file>
@@ -533,7 +493,7 @@
     <col min="3" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -784,98 +744,6 @@
       </c>
       <c r="G11" s="2" t="s">
         <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB07F632-1C14-4845-B68C-BC5D27020286}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="2">
-        <v>82.5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="2">
-        <v>75</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="2">
-        <v>90</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="2">
-        <v>77.5</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="2">
-        <v>85</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="1">
-        <v>82</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
